--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -699,12 +699,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3661,12 +3661,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I89" s="2"/>
@@ -4160,12 +4160,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I103" s="2"/>
@@ -4195,12 +4195,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I104" s="2"/>
@@ -4230,12 +4230,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I105" s="2"/>
@@ -5964,7 +5964,7 @@
       <c r="Q6" s="10"/>
       <c r="R6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S6" s="10"/>
@@ -6024,7 +6024,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S7" s="8"/>
@@ -6045,7 +6045,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="9"/>
@@ -6064,7 +6064,7 @@
       <c r="K8" s="9"/>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M8" s="9"/>
@@ -6077,13 +6077,13 @@
       <c r="O8" s="9"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S8" s="9"/>
@@ -6104,7 +6104,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G9" s="9"/>
@@ -6122,7 +6122,7 @@
       <c r="K9" s="9"/>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M9" s="9"/>
@@ -6134,13 +6134,13 @@
       <c r="O9" s="9"/>
       <c r="P9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q9" s="9"/>
       <c r="R9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S9" s="9"/>
@@ -6161,25 +6161,25 @@
       <c r="E10" s="10"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="10"/>
@@ -6191,7 +6191,7 @@
       <c r="O10" s="10"/>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q10" s="10"/>

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5687,995 +5725,995 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="E3" s="24"/>
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="24"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="K3" s="22"/>
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="M3" s="24"/>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="Q3" s="22"/>
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="S3" s="8"/>
+      <c r="S3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
+      <c r="S4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="25"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="25"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="25"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="25"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="25"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 姑</t>
         </is>
       </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="25"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S5" s="9"/>
+      <c r="S5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="26"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="26"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="26"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="26"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="M6" s="26"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="O6" s="26"/>
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="Q6" s="26"/>
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S6" s="10"/>
+      <c r="S6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="22"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="22"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="22"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="22"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="Q7" s="22"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S7" s="8"/>
+      <c r="S7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="25"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="25"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="M8" s="25"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="25"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="Q8" s="25"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S8" s="9"/>
+      <c r="S8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="25"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="25"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="25"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="25"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="O9" s="25"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="25"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S9" s="9"/>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="26"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="26"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="26"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="Q10" s="26"/>
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S10" s="10"/>
+      <c r="S10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="22"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="22"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="O11" s="8"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="22"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="22"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 仲</t>
         </is>
       </c>
-      <c r="S11" s="8"/>
+      <c r="S11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="25"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="25"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="M12" s="25"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="25"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="Q12" s="25"/>
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="S12" s="9"/>
+      <c r="S12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
+      <c r="S13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 太</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="Q14" s="26"/>
+      <c r="R14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="S14" s="13"/>
+      <c r="S14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="22"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="I15" s="22"/>
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="K15" s="22"/>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="M15" s="22"/>
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="O15" s="22"/>
+      <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="17" t="inlineStr">
+      <c r="Q15" s="22"/>
+      <c r="R15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="S15" s="8"/>
+      <c r="S15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="I16" s="25"/>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="K16" s="25"/>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="M16" s="25"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="17" t="inlineStr">
+      <c r="O16" s="25"/>
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="17" t="inlineStr">
+      <c r="Q16" s="25"/>
+      <c r="R16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="S16" s="9"/>
+      <c r="S16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="I17" s="25"/>
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="K17" s="25"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="M17" s="25"/>
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="O17" s="25"/>
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="Q17" s="25"/>
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="S17" s="9"/>
+      <c r="S17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="26"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="26"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="26"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="K18" s="26"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="M18" s="26"/>
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="O18" s="26"/>
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="18" t="inlineStr">
+      <c r="Q18" s="26"/>
+      <c r="R18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S18" s="13"/>
+      <c r="S18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -5700,30 +5700,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5942,12 +5942,12 @@
       <c r="Q5" s="25"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="S6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="22"/>
@@ -6038,7 +6038,7 @@
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -6056,7 +6056,7 @@
       <c r="O7" s="22"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
       <c r="I8" s="25"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="25"/>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="S8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
       <c r="I9" s="25"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K9" s="25"/>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="S10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="S14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -331,7 +331,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">144</t>
+          <t xml:space="preserve">152</t>
         </is>
       </c>
     </row>
@@ -343,7 +343,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
     </row>
@@ -379,7 +379,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
+          <t xml:space="preserve">번호칸 2곳 처리 확인</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16정간·굵은 선 4칸마다. 손채보 자진모리. 가사 칸은 저작권 보호 범위 재구성 우려로 비움(사용자 원자료에서 직접 채울 것). 율명·기호만 전사. 왼쪽 끝 번호칸(1·2·3·4·절)은 절 표시로 보여 본문 줄에 포함하지 않음.</t>
+          <t xml:space="preserve">16정간·굵은 선 4칸마다(원본 4단×4정간, 세로 줄이 단을 이어 내려감). 손채보 자진모리. 10줄. 율명·가사 재판독(10-12). 박 세는 번호칸(1·2·3·4) 두 곳(5줄 5~8정간, 8줄 1~4정간)은 율명 없이 비우고 노란 칸으로 표시.</t>
         </is>
       </c>
     </row>
@@ -595,16 +595,21 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I2" s="2"/>
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
@@ -631,16 +636,21 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|㳞</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">㳞
+–
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시요</t>
+        </is>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
@@ -877,53 +887,62 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞|仲</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
-        </is>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <v>3</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|㳞</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사시요</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -950,15 +969,21 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
@@ -983,23 +1008,22 @@
       <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌|㴌</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-㴌</t>
-        </is>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1025,16 +1049,21 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲</t>
+          <t xml:space="preserve">姑|姑|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
@@ -1061,16 +1090,21 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1097,16 +1131,21 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-無</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1131,22 +1170,24 @@
       <c r="F17" s="2">
         <v>4</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">? 흐려 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|無|–</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1182,7 +1223,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1209,17 +1254,21 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|仲</t>
+          <t xml:space="preserve">無|南|仲</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
+南
 仲</t>
         </is>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑의</t>
+        </is>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1246,16 +1295,21 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|姑</t>
+          <t xml:space="preserve">姑|仲|姑</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">姑
+仲
 姑</t>
         </is>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이로</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1282,16 +1336,21 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구나</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1318,12 +1377,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1423,12 +1482,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1458,16 +1517,21 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃바</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1494,15 +1558,21 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|㳞|㴌</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">–
+㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구니</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1529,16 +1599,21 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들러</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1565,16 +1640,21 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|太</t>
+          <t xml:space="preserve">–|㳞|㴌</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-太</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">–
+㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메고</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1601,16 +1681,21 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃팔</t>
+        </is>
+      </c>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
@@ -1637,15 +1722,20 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">–
+㳞</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">러</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1672,16 +1762,21 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">㴌|㴌|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
+          <t xml:space="preserve">㴌
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나왔</t>
+        </is>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
@@ -1708,15 +1803,19 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I33" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
       <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
@@ -1743,16 +1842,21 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I34" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">붉은</t>
+        </is>
+      </c>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1779,15 +1883,20 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
+          <t xml:space="preserve">–
+㳞</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
@@ -1814,16 +1923,21 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">湳|㳞|–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
+          <t xml:space="preserve">湳
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파란</t>
+        </is>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
@@ -1850,15 +1964,19 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
@@ -1885,16 +2003,26 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="4"/>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노랗</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">첫 글자 潢/無 흐림</t>
+        </is>
+      </c>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -1920,17 +2048,26 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="4"/>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고도</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢/無 흐림</t>
+        </is>
+      </c>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -1956,15 +2093,21 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하얀</t>
+        </is>
+      </c>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -1991,15 +2134,19 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I41" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2026,16 +2173,21 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남색</t>
+        </is>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
@@ -2062,16 +2214,21 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|㳞</t>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">㳞
+㳞
 㳞</t>
         </is>
       </c>
-      <c r="I43" s="2"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자색에</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2098,15 +2255,21 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연분</t>
+        </is>
+      </c>
       <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
@@ -2131,22 +2294,22 @@
       <c r="F45" s="2">
         <v>3</v>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">? 흘림</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홍</t>
+        </is>
+      </c>
+      <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
     <row r="46">
@@ -2172,15 +2335,21 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울긋</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2207,15 +2376,21 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
+          <t xml:space="preserve">無
+–
+無</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불긋</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2242,15 +2417,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빛난</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2285,7 +2465,11 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I49" s="2"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2310,59 +2494,64 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|潢</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">? 南은 南 흘림일 수 있음</t>
-        </is>
-      </c>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2">
-        <v>4</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2</v>
-      </c>
-      <c r="F51" s="2">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無|潢</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="I51" s="2"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아롱</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南|仲</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다롱의</t>
+        </is>
+      </c>
       <c r="J51" s="4"/>
       <c r="K51" s="2"/>
     </row>
@@ -2389,17 +2578,21 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|仲</t>
+          <t xml:space="preserve">姑|仲|姑</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="I52" s="2"/>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고운</t>
+        </is>
+      </c>
       <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
@@ -2426,16 +2619,19 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I53" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
@@ -2462,15 +2658,21 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
@@ -2497,15 +2699,21 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|㳞|㳞</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I55" s="2"/>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시요</t>
+        </is>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
@@ -2532,15 +2740,21 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2602,15 +2816,21 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2637,16 +2857,21 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|仲</t>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-仲</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사시요</t>
+        </is>
+      </c>
       <c r="J59" s="4"/>
       <c r="K59" s="2"/>
     </row>
@@ -2673,16 +2898,21 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2709,15 +2939,19 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2744,15 +2978,21 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑|姑|–</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J62" s="4"/>
       <c r="K62" s="2"/>
     </row>
@@ -2779,15 +3019,21 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I63" s="2"/>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
@@ -2814,15 +3060,21 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I64" s="2"/>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -2849,15 +3101,21 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I65" s="2"/>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -2894,7 +3152,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I66" s="2"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -2921,17 +3183,21 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑|仲</t>
+          <t xml:space="preserve">無|南|仲</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
+南
 仲</t>
         </is>
       </c>
-      <c r="I67" s="2"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑의</t>
+        </is>
+      </c>
       <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
@@ -2958,16 +3224,21 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">姑|仲|姑</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이로</t>
+        </is>
+      </c>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
@@ -2994,15 +3265,21 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I69" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구나</t>
+        </is>
+      </c>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3027,18 +3304,14 @@
       <c r="F70" s="2">
         <v>2</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="4"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음 (아래 '2절')</t>
+        </is>
+      </c>
       <c r="K70" s="2"/>
     </row>
     <row r="71">
@@ -3062,18 +3335,14 @@
       <c r="F71" s="2">
         <v>2</v>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K71" s="2"/>
     </row>
     <row r="72">
@@ -3097,18 +3366,14 @@
       <c r="F72" s="2">
         <v>2</v>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
       <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K72" s="2"/>
     </row>
     <row r="73">
@@ -3132,18 +3397,14 @@
       <c r="F73" s="2">
         <v>2</v>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
       <c r="I73" s="2"/>
-      <c r="J73" s="4"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K73" s="2"/>
     </row>
     <row r="74">
@@ -3169,16 +3430,21 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I74" s="2"/>
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉올</t>
+        </is>
+      </c>
       <c r="J74" s="4"/>
       <c r="K74" s="2"/>
     </row>
@@ -3205,15 +3471,21 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞|㳞|–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I75" s="2"/>
+          <t xml:space="preserve">㳞
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉올</t>
+        </is>
+      </c>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
@@ -3240,15 +3512,21 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I76" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">맺힌</t>
+        </is>
+      </c>
       <c r="J76" s="4"/>
       <c r="K76" s="2"/>
     </row>
@@ -3275,15 +3553,19 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I77" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J77" s="4"/>
       <c r="K77" s="2"/>
     </row>
@@ -3310,15 +3592,21 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㳞|㴌|–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숭얼</t>
+        </is>
+      </c>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3345,16 +3633,26 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南|–|無</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
-      <c r="J79" s="4"/>
+          <t xml:space="preserve">南
+–
+無</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숭얼의</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 송엽?/숭얼 흐림</t>
+        </is>
+      </c>
       <c r="K79" s="2"/>
     </row>
     <row r="80">
@@ -3380,15 +3678,21 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無|–|潢</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I80" s="2"/>
+          <t xml:space="preserve">無
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달린</t>
+        </is>
+      </c>
       <c r="J80" s="4"/>
       <c r="K80" s="2"/>
     </row>
@@ -3415,15 +3719,19 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I81" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
@@ -3450,16 +3758,21 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞</t>
+          <t xml:space="preserve">南|–|無</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="I82" s="2"/>
+          <t xml:space="preserve">南
+–
+無</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방실</t>
+        </is>
+      </c>
       <c r="J82" s="4"/>
       <c r="K82" s="2"/>
     </row>
@@ -3486,16 +3799,21 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">潢|–|潢</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I83" s="2"/>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방실</t>
+        </is>
+      </c>
       <c r="J83" s="4"/>
       <c r="K83" s="2"/>
     </row>
@@ -3522,15 +3840,21 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I84" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웃는</t>
+        </is>
+      </c>
       <c r="J84" s="4"/>
       <c r="K84" s="2"/>
     </row>
@@ -3557,15 +3881,19 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I85" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J85" s="4"/>
       <c r="K85" s="2"/>
     </row>
@@ -3592,16 +3920,21 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㴌
+–
 㳞</t>
         </is>
       </c>
-      <c r="I86" s="2"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활짝</t>
+        </is>
+      </c>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3628,16 +3961,21 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞</t>
+          <t xml:space="preserve">㳞|㳞|㴌</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="I87" s="2"/>
+㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피었네</t>
+        </is>
+      </c>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
@@ -3664,15 +4002,21 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢|–|㴌</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I88" s="2"/>
+          <t xml:space="preserve">潢
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다핀</t>
+        </is>
+      </c>
       <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
@@ -3699,15 +4043,20 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞|△</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I89" s="2"/>
+          <t xml:space="preserve">㳞
+△</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J89" s="4"/>
       <c r="K89" s="2"/>
     </row>
@@ -3734,15 +4083,21 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌|–|汰</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I90" s="2"/>
+          <t xml:space="preserve">㴌
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">벌</t>
+        </is>
+      </c>
       <c r="J90" s="4"/>
       <c r="K90" s="2"/>
     </row>
@@ -3769,15 +4124,21 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">汰|–|汰</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I91" s="2"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모아</t>
+        </is>
+      </c>
       <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
@@ -3804,16 +4165,21 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑</t>
+          <t xml:space="preserve">汰|汰|汰</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="I92" s="2"/>
+          <t xml:space="preserve">汰
+汰
+汰</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노래한</t>
+        </is>
+      </c>
       <c r="J92" s="4"/>
       <c r="K92" s="2"/>
     </row>
@@ -3840,15 +4206,19 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I93" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J93" s="4"/>
       <c r="K93" s="2"/>
     </row>
@@ -3875,15 +4245,21 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">汰|–|汰</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I94" s="2"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나비</t>
+        </is>
+      </c>
       <c r="J94" s="4"/>
       <c r="K94" s="2"/>
     </row>
@@ -3910,15 +4286,21 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌|–|南</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I95" s="2"/>
+          <t xml:space="preserve">㴌
+–
+南</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앉아</t>
+        </is>
+      </c>
       <c r="J95" s="4"/>
       <c r="K95" s="2"/>
     </row>
@@ -3945,15 +4327,21 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">汰|–|汰</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I96" s="2"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춤추는</t>
+        </is>
+      </c>
       <c r="J96" s="4"/>
       <c r="K96" s="2"/>
     </row>
@@ -3980,15 +4368,20 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南|△</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I97" s="2"/>
+          <t xml:space="preserve">南
+△</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J97" s="4"/>
       <c r="K97" s="2"/>
     </row>
@@ -4013,23 +4406,24 @@
       <c r="F98" s="2">
         <v>1</v>
       </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|潢</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="I98" s="3"/>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">? 南은 南 흘림일 수 있음</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|–|㳞</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
+      <c r="J98" s="4"/>
       <c r="K98" s="2"/>
     </row>
     <row r="99">
@@ -4055,16 +4449,21 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">–|㳞|㳞</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I99" s="2"/>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시요</t>
+        </is>
+      </c>
       <c r="J99" s="4"/>
       <c r="K99" s="2"/>
     </row>
@@ -4091,16 +4490,21 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="I100" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J100" s="4"/>
       <c r="K100" s="2"/>
     </row>
@@ -4127,13 +4531,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I101" s="2"/>
@@ -4163,15 +4566,21 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I102" s="2"/>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
     </row>
@@ -4198,15 +4607,21 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I103" s="2"/>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사시요</t>
+        </is>
+      </c>
       <c r="J103" s="4"/>
       <c r="K103" s="2"/>
     </row>
@@ -4233,15 +4648,21 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I104" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
       <c r="J104" s="4"/>
       <c r="K104" s="2"/>
     </row>
@@ -4268,15 +4689,20 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|△</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I105" s="2"/>
+          <t xml:space="preserve">潢
+△</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J105" s="4"/>
       <c r="K105" s="2"/>
     </row>
@@ -4303,15 +4729,21 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑|姑|–</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I106" s="2"/>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J106" s="4"/>
       <c r="K106" s="2"/>
     </row>
@@ -4338,15 +4770,21 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲|仲|–</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I107" s="2"/>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J107" s="4"/>
       <c r="K107" s="2"/>
     </row>
@@ -4373,15 +4811,21 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I108" s="2"/>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J108" s="4"/>
       <c r="K108" s="2"/>
     </row>
@@ -4408,15 +4852,21 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|無|–</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I109" s="2"/>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J109" s="4"/>
       <c r="K109" s="2"/>
     </row>
@@ -4443,15 +4893,21 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">潢|無|潢</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I110" s="2"/>
+          <t xml:space="preserve">潢
+無
+潢</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J110" s="4"/>
       <c r="K110" s="2"/>
     </row>
@@ -4478,15 +4934,21 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無|南|仲</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I111" s="2"/>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑의</t>
+        </is>
+      </c>
       <c r="J111" s="4"/>
       <c r="K111" s="2"/>
     </row>
@@ -4513,15 +4975,21 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑|仲|姑</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I112" s="2"/>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이로</t>
+        </is>
+      </c>
       <c r="J112" s="4"/>
       <c r="K112" s="2"/>
     </row>
@@ -4548,15 +5016,21 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I113" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구나</t>
+        </is>
+      </c>
       <c r="J113" s="4"/>
       <c r="K113" s="2"/>
     </row>
@@ -4581,21 +5055,12 @@
       <c r="F114" s="2">
         <v>1</v>
       </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|㳞</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="I114" s="3"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">? 흘림, 㳞은 氵+酉 형태</t>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
         </is>
       </c>
       <c r="K114" s="2"/>
@@ -4621,19 +5086,14 @@
       <c r="F115" s="2">
         <v>1</v>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太|汰</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
       <c r="I115" s="2"/>
-      <c r="J115" s="4"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K115" s="2"/>
     </row>
     <row r="116">
@@ -4657,18 +5117,14 @@
       <c r="F116" s="2">
         <v>1</v>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-      <c r="J116" s="4"/>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K116" s="2"/>
     </row>
     <row r="117">
@@ -4692,18 +5148,14 @@
       <c r="F117" s="2">
         <v>1</v>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="4"/>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 박 세는 번호칸(1·2·3·4) — 앞 음 늘임/쉼으로 보임, 율명 없음</t>
+        </is>
+      </c>
       <c r="K117" s="2"/>
     </row>
     <row r="118">
@@ -4729,16 +5181,21 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太|汰</t>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="I118" s="2"/>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이송이</t>
+        </is>
+      </c>
       <c r="J118" s="4"/>
       <c r="K118" s="2"/>
     </row>
@@ -4765,15 +5222,21 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㳞|–|㴌</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I119" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저송이</t>
+        </is>
+      </c>
       <c r="J119" s="4"/>
       <c r="K119" s="2"/>
     </row>
@@ -4800,15 +5263,21 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無|–|㴌</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I120" s="2"/>
+          <t xml:space="preserve">無
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각꽃</t>
+        </is>
+      </c>
       <c r="J120" s="4"/>
       <c r="K120" s="2"/>
     </row>
@@ -4835,15 +5304,21 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㳞|㴌|–</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I121" s="2"/>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">송이</t>
+        </is>
+      </c>
       <c r="J121" s="4"/>
       <c r="K121" s="2"/>
     </row>
@@ -4870,16 +5345,21 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">無|–|無</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I122" s="2"/>
+          <t xml:space="preserve">無
+–
+無</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">향기</t>
+        </is>
+      </c>
       <c r="J122" s="4"/>
       <c r="K122" s="2"/>
     </row>
@@ -4906,15 +5386,21 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌|–|㴌</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I123" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가풍</t>
+        </is>
+      </c>
       <c r="J123" s="4"/>
       <c r="K123" s="2"/>
     </row>
@@ -4941,15 +5427,21 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㴌|㴌|–</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I124" s="2"/>
+          <t xml:space="preserve">㴌
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겨나온</t>
+        </is>
+      </c>
       <c r="J124" s="4"/>
       <c r="K124" s="2"/>
     </row>
@@ -4976,15 +5468,20 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">無|△</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I125" s="2"/>
+          <t xml:space="preserve">無
+△</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J125" s="4"/>
       <c r="K125" s="2"/>
     </row>
@@ -5011,15 +5508,21 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I126" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이꽃</t>
+        </is>
+      </c>
       <c r="J126" s="4"/>
       <c r="K126" s="2"/>
     </row>
@@ -5046,15 +5549,21 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I127" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저꽃</t>
+        </is>
+      </c>
       <c r="J127" s="4"/>
       <c r="K127" s="2"/>
     </row>
@@ -5081,16 +5590,26 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">湳|–|㳞</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I128" s="2"/>
-      <c r="J128" s="4"/>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각꽃</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 가/각 흐림</t>
+        </is>
+      </c>
       <c r="K128" s="2"/>
     </row>
     <row r="129">
@@ -5116,15 +5635,21 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|㳞|–</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I129" s="2"/>
+          <t xml:space="preserve">㳞
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이꽃</t>
+        </is>
+      </c>
       <c r="J129" s="4"/>
       <c r="K129" s="2"/>
     </row>
@@ -5151,16 +5676,21 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞</t>
+          <t xml:space="preserve">汰|–|汰</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="I130" s="2"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해당</t>
+        </is>
+      </c>
       <c r="J130" s="4"/>
       <c r="K130" s="2"/>
     </row>
@@ -5187,17 +5717,25 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|仲</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I131" s="2"/>
-      <c r="J131" s="4"/>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 아래 글자 㴌? 흐림</t>
+        </is>
+      </c>
       <c r="K131" s="2"/>
     </row>
     <row r="132">
@@ -5223,15 +5761,21 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">汰|汰|–</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I132" s="2"/>
+          <t xml:space="preserve">汰
+汰
+–</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모란</t>
+        </is>
+      </c>
       <c r="J132" s="4"/>
       <c r="K132" s="2"/>
     </row>
@@ -5258,15 +5802,19 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I133" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="J133" s="4"/>
       <c r="K133" s="2"/>
     </row>
@@ -5293,16 +5841,21 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑</t>
+          <t xml:space="preserve">汰|–|汰</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="I134" s="2"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난초</t>
+        </is>
+      </c>
       <c r="J134" s="4"/>
       <c r="K134" s="2"/>
     </row>
@@ -5329,15 +5882,21 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南|–|南</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I135" s="2"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지초</t>
+        </is>
+      </c>
       <c r="J135" s="4"/>
       <c r="K135" s="2"/>
     </row>
@@ -5364,15 +5923,21 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">南|–|汰</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I136" s="2"/>
+          <t xml:space="preserve">南
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">온갖</t>
+        </is>
+      </c>
       <c r="J136" s="4"/>
       <c r="K136" s="2"/>
     </row>
@@ -5399,15 +5964,21 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌|–|汰</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I137" s="2"/>
+          <t xml:space="preserve">㴌
+–
+汰</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">향초</t>
+        </is>
+      </c>
       <c r="J137" s="4"/>
       <c r="K137" s="2"/>
     </row>
@@ -5434,15 +6005,21 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㳞|㴌|–</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I138" s="2"/>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작약</t>
+        </is>
+      </c>
       <c r="J138" s="4"/>
       <c r="K138" s="2"/>
     </row>
@@ -5469,15 +6046,21 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">汰|–|南</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I139" s="2"/>
+          <t xml:space="preserve">汰
+–
+南</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모란의</t>
+        </is>
+      </c>
       <c r="J139" s="4"/>
       <c r="K139" s="2"/>
     </row>
@@ -5504,15 +6087,21 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">汰|–|㴌</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I140" s="2"/>
+          <t xml:space="preserve">汰
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장미</t>
+        </is>
+      </c>
       <c r="J140" s="4"/>
       <c r="K140" s="2"/>
     </row>
@@ -5539,15 +6128,19 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I141" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
       <c r="J141" s="4"/>
       <c r="K141" s="2"/>
     </row>
@@ -5574,15 +6167,21 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌|–|㳞</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I142" s="2"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J142" s="4"/>
       <c r="K142" s="2"/>
     </row>
@@ -5609,15 +6208,21 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–|㳞|㳞</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I143" s="2"/>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시요</t>
+        </is>
+      </c>
       <c r="J143" s="4"/>
       <c r="K143" s="2"/>
     </row>
@@ -5644,15 +6249,21 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">㳞|–|㳞</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I144" s="2"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃사</t>
+        </is>
+      </c>
       <c r="J144" s="4"/>
       <c r="K144" s="2"/>
     </row>
@@ -5679,20 +6290,653 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I145" s="2"/>
       <c r="J145" s="4"/>
       <c r="K145" s="2"/>
     </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>1</v>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C146" s="2">
+        <v>10</v>
+      </c>
+      <c r="D146" s="2">
+        <v>10</v>
+      </c>
+      <c r="E146" s="2">
+        <v>1</v>
+      </c>
+      <c r="F146" s="2">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳|–|㳞</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
+      <c r="J146" s="4"/>
+      <c r="K146" s="2"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>1</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C147" s="2">
+        <v>10</v>
+      </c>
+      <c r="D147" s="2">
+        <v>10</v>
+      </c>
+      <c r="E147" s="2">
+        <v>2</v>
+      </c>
+      <c r="F147" s="2">
+        <v>1</v>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㳞|㳞</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사시요</t>
+        </is>
+      </c>
+      <c r="J147" s="4"/>
+      <c r="K147" s="2"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
+        <v>1</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C148" s="2">
+        <v>10</v>
+      </c>
+      <c r="D148" s="2">
+        <v>10</v>
+      </c>
+      <c r="E148" s="2">
+        <v>3</v>
+      </c>
+      <c r="F148" s="2">
+        <v>1</v>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|–|㳞</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃을</t>
+        </is>
+      </c>
+      <c r="J148" s="4"/>
+      <c r="K148" s="2"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>1</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C149" s="2">
+        <v>10</v>
+      </c>
+      <c r="D149" s="2">
+        <v>10</v>
+      </c>
+      <c r="E149" s="2">
+        <v>4</v>
+      </c>
+      <c r="F149" s="2">
+        <v>1</v>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J149" s="4"/>
+      <c r="K149" s="2"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>1</v>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C150" s="2">
+        <v>10</v>
+      </c>
+      <c r="D150" s="2">
+        <v>10</v>
+      </c>
+      <c r="E150" s="2">
+        <v>5</v>
+      </c>
+      <c r="F150" s="2">
+        <v>2</v>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|姑|–</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J150" s="4"/>
+      <c r="K150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>1</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C151" s="2">
+        <v>10</v>
+      </c>
+      <c r="D151" s="2">
+        <v>10</v>
+      </c>
+      <c r="E151" s="2">
+        <v>6</v>
+      </c>
+      <c r="F151" s="2">
+        <v>2</v>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|仲|–</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J151" s="4"/>
+      <c r="K151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
+        <v>1</v>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C152" s="2">
+        <v>10</v>
+      </c>
+      <c r="D152" s="2">
+        <v>10</v>
+      </c>
+      <c r="E152" s="2">
+        <v>7</v>
+      </c>
+      <c r="F152" s="2">
+        <v>2</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|南|–</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J152" s="4"/>
+      <c r="K152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>1</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C153" s="2">
+        <v>10</v>
+      </c>
+      <c r="D153" s="2">
+        <v>10</v>
+      </c>
+      <c r="E153" s="2">
+        <v>8</v>
+      </c>
+      <c r="F153" s="2">
+        <v>2</v>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|無</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J153" s="4"/>
+      <c r="K153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2">
+        <v>1</v>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C154" s="2">
+        <v>10</v>
+      </c>
+      <c r="D154" s="2">
+        <v>10</v>
+      </c>
+      <c r="E154" s="2">
+        <v>9</v>
+      </c>
+      <c r="F154" s="2">
+        <v>3</v>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無|潢</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無
+潢</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
+      <c r="J154" s="4"/>
+      <c r="K154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2">
+        <v>1</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C155" s="2">
+        <v>10</v>
+      </c>
+      <c r="D155" s="2">
+        <v>10</v>
+      </c>
+      <c r="E155" s="2">
+        <v>10</v>
+      </c>
+      <c r="F155" s="2">
+        <v>3</v>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|南|仲</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑의</t>
+        </is>
+      </c>
+      <c r="J155" s="4"/>
+      <c r="K155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2">
+        <v>1</v>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C156" s="2">
+        <v>10</v>
+      </c>
+      <c r="D156" s="2">
+        <v>10</v>
+      </c>
+      <c r="E156" s="2">
+        <v>11</v>
+      </c>
+      <c r="F156" s="2">
+        <v>3</v>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|仲|姑</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이로</t>
+        </is>
+      </c>
+      <c r="J156" s="4"/>
+      <c r="K156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2">
+        <v>1</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C157" s="2">
+        <v>10</v>
+      </c>
+      <c r="D157" s="2">
+        <v>10</v>
+      </c>
+      <c r="E157" s="2">
+        <v>12</v>
+      </c>
+      <c r="F157" s="2">
+        <v>3</v>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–|南</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구나</t>
+        </is>
+      </c>
+      <c r="J157" s="4"/>
+      <c r="K157" s="2"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2">
+        <v>1</v>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C158" s="2">
+        <v>10</v>
+      </c>
+      <c r="D158" s="2">
+        <v>10</v>
+      </c>
+      <c r="E158" s="2">
+        <v>13</v>
+      </c>
+      <c r="F158" s="2">
+        <v>4</v>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I158" s="2"/>
+      <c r="J158" s="4"/>
+      <c r="K158" s="2"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2">
+        <v>1</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C159" s="2">
+        <v>10</v>
+      </c>
+      <c r="D159" s="2">
+        <v>10</v>
+      </c>
+      <c r="E159" s="2">
+        <v>14</v>
+      </c>
+      <c r="F159" s="2">
+        <v>4</v>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I159" s="2"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="2"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2">
+        <v>1</v>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C160" s="2">
+        <v>10</v>
+      </c>
+      <c r="D160" s="2">
+        <v>10</v>
+      </c>
+      <c r="E160" s="2">
+        <v>15</v>
+      </c>
+      <c r="F160" s="2">
+        <v>4</v>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I160" s="2"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="2"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2">
+        <v>1</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/꽃 타령.png</t>
+        </is>
+      </c>
+      <c r="C161" s="2">
+        <v>10</v>
+      </c>
+      <c r="D161" s="2">
+        <v>10</v>
+      </c>
+      <c r="E161" s="2">
+        <v>16</v>
+      </c>
+      <c r="F161" s="2">
+        <v>4</v>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I161" s="2"/>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본: 끝에 ○ 표시</t>
+        </is>
+      </c>
+      <c r="K161" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K145"/>
+  <autoFilter ref="A1:K161"/>
 </worksheet>
 </file>
 
@@ -5718,6 +6962,8 @@
     <col min="17" max="17" width="6" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
+    <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5747,977 +6993,1893 @@
       <c r="Q2" s="20"/>
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">湳
+–
 㳞</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-㳞</t>
-        </is>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해
+당</t>
+        </is>
+      </c>
+      <c r="F3" s="23"/>
       <c r="G3" s="24"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㴌
+–
 㳞</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
       <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+無</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방
+실</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="M3" s="24"/>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="O3" s="22"/>
-      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="Q3" s="22"/>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+롱</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">붉
+은</t>
+        </is>
+      </c>
       <c r="R3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">潢
+無
+潢</t>
+        </is>
+      </c>
+      <c r="S3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="S3" s="22"/>
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="U3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+시
+요</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="F4" s="23"/>
       <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시
+요</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">방
+실</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑
+의</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다
+롱
+의</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㳞</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="S4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑
+의</t>
+        </is>
+      </c>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="21" t="inlineStr">
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="U4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시
+요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="82.06" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+汰
+–</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모
+란</t>
+        </is>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웃
+는</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+이
+로</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고
+운</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="Q5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파
+란</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="S5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+이
+로</t>
+        </is>
+      </c>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U5" s="25"/>
+    </row>
+    <row r="6" ht="82.06" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I6" s="26"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+나</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="Q6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="S6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+나</t>
+        </is>
+      </c>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U6" s="26"/>
+    </row>
+    <row r="7" ht="82.06" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난
+초</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+송
+이</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활
+짝</t>
+        </is>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="O7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="Q7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노
+랗</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S7" s="22"/>
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U7" s="22"/>
+    </row>
+    <row r="8" ht="82.06" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+초</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저
+송
+이</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+시
+요</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">피
+었
+네</t>
+        </is>
+      </c>
+      <c r="L8" s="23"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="O8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시
+요</t>
+        </is>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+潢</t>
+        </is>
+      </c>
+      <c r="Q8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고
+도</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S8" s="25"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U8" s="25"/>
+    </row>
+    <row r="9" ht="82.06" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+汰</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">온
+갖</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="21" t="inlineStr">
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각
+꽃</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다
+핀</t>
+        </is>
+      </c>
+      <c r="L9" s="23"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="O9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="Q9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하
+얀</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S9" s="25"/>
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U9" s="25"/>
+    </row>
+    <row r="10" ht="82.06" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+汰</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">향
+초</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">송
+이</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+△</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+△</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="L10" s="23"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O10" s="26"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="S10" s="26"/>
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="U10" s="26"/>
+    </row>
+    <row r="11" ht="82.06" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O4" s="25"/>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작
+약</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
+–
+無</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">향
+기</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
 姑
-仲</t>
-        </is>
-      </c>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
+–</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+汰</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">벌</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–
 㳞</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
-    </row>
-    <row r="5" ht="82.06" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="M5" s="25"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="O5" s="25"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S5" s="25"/>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O6" s="26"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S6" s="26"/>
-    </row>
-    <row r="7" ht="82.06" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
+      <c r="M11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉
+올</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="22"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K7" s="22"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M7" s="22"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S7" s="22"/>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
+      <c r="O11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M8" s="25"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S8" s="25"/>
-    </row>
-    <row r="9" ht="82.06" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M9" s="25"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O9" s="25"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S9" s="25"/>
-    </row>
-    <row r="10" ht="82.06" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I10" s="26"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="O10" s="26"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="S10" s="26"/>
-    </row>
-    <row r="11" ht="82.06" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M11" s="22"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="O11" s="22"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="Q11" s="22"/>
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남
+색</t>
+        </is>
+      </c>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-㳞
-仲</t>
-        </is>
-      </c>
-      <c r="S11" s="22"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="S11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+바</t>
+        </is>
+      </c>
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="U11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C12" s="25"/>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑
+의</t>
+        </is>
+      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="25"/>
+          <t xml:space="preserve">汰
+–
+南</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모
+란
+의</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G12" s="25"/>
+          <t xml:space="preserve">㴌
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+풍</t>
+        </is>
+      </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I12" s="25"/>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="25"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모
+아</t>
+        </is>
+      </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-仲</t>
-        </is>
-      </c>
-      <c r="M12" s="25"/>
+          <t xml:space="preserve">㳞
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉
+올</t>
+        </is>
+      </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">㳞
+㳞
 㳞</t>
         </is>
       </c>
-      <c r="O12" s="25"/>
+      <c r="O12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+시
+요</t>
+        </is>
+      </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q12" s="25"/>
+          <t xml:space="preserve">㳞
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="Q12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자
+색
+에</t>
+        </is>
+      </c>
       <c r="R12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="S12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+니</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞
+㳞
 㳞</t>
         </is>
       </c>
-      <c r="S12" s="25"/>
+      <c r="U12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+시
+요</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C13" s="25"/>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+이
+로</t>
+        </is>
+      </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E13" s="25"/>
+          <t xml:space="preserve">汰
+–
+㴌</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장
+미</t>
+        </is>
+      </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="25"/>
+          <t xml:space="preserve">㴌
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">겨
+나
+온</t>
+        </is>
+      </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="I13" s="25"/>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K13" s="25"/>
+          <t xml:space="preserve">汰
+汰
+汰</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노
+래
+한</t>
+        </is>
+      </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="M13" s="25"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">맺
+힌</t>
+        </is>
+      </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O13" s="25"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="Q13" s="25"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연
+분</t>
+        </is>
+      </c>
       <c r="R13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="S13" s="25"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="S13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들
+러</t>
+        </is>
+      </c>
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="U13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+을</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C14" s="26"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+나</t>
+        </is>
+      </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="26"/>
+          <t xml:space="preserve">無
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="26"/>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K14" s="26"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M14" s="26"/>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O14" s="27"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-太</t>
-        </is>
-      </c>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홍</t>
+        </is>
+      </c>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㳞
 㴌</t>
         </is>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메
+고</t>
+        </is>
+      </c>
+      <c r="T14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="U14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E15" s="22"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G15" s="22"/>
+          <t xml:space="preserve">㴌
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+꽃</t>
+        </is>
+      </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I15" s="22"/>
+          <t xml:space="preserve">潢
+無
+潢</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K15" s="22"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+비</t>
+        </is>
+      </c>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M15" s="22"/>
+          <t xml:space="preserve">㳞
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="M15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숭
+얼</t>
+        </is>
+      </c>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O15" s="22"/>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="O15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="P15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="Q15" s="22"/>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울
+긋</t>
+        </is>
+      </c>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="S15" s="22"/>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+팔</t>
+        </is>
+      </c>
+      <c r="T15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="U15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E16" s="25"/>
+          <t xml:space="preserve">–
+㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시
+요</t>
+        </is>
+      </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G16" s="25"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저
+꽃</t>
+        </is>
+      </c>
       <c r="H16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I16" s="25"/>
+          <t xml:space="preserve">無
+南
+仲</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑
+의</t>
+        </is>
+      </c>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K16" s="25"/>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M16" s="25"/>
+          <t xml:space="preserve">㴌
+–
+南</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앉
+아</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+無</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숭
+얼
+의</t>
+        </is>
+      </c>
       <c r="N16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O16" s="25"/>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="P16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q16" s="25"/>
+          <t xml:space="preserve">無
+–
+無</t>
+        </is>
+      </c>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불
+긋</t>
+        </is>
+      </c>
       <c r="R16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="S16" s="25"/>
+          <t xml:space="preserve">–
+㳞</t>
+        </is>
+      </c>
+      <c r="S16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">러</t>
+        </is>
+      </c>
+      <c r="T16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲
+–</t>
+        </is>
+      </c>
+      <c r="U16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G17" s="25"/>
+          <t xml:space="preserve">㳞
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+사</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–
+㳞</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각
+꽃</t>
+        </is>
+      </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I17" s="25"/>
+          <t xml:space="preserve">姑
+仲
+姑</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃
+이
+로</t>
+        </is>
+      </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K17" s="25"/>
+          <t xml:space="preserve">汰
+–
+汰</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춤
+추
+는</t>
+        </is>
+      </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M17" s="25"/>
+          <t xml:space="preserve">無
+–
+潢</t>
+        </is>
+      </c>
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달
+린</t>
+        </is>
+      </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O17" s="25"/>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="O17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-汰</t>
-        </is>
-      </c>
-      <c r="Q17" s="25"/>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="Q17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빛
+난</t>
+        </is>
+      </c>
       <c r="R17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-無</t>
-        </is>
-      </c>
-      <c r="S17" s="25"/>
+          <t xml:space="preserve">㴌
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="S17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+왔</t>
+        </is>
+      </c>
+      <c r="T17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南
+–</t>
+        </is>
+      </c>
+      <c r="U17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C18" s="26"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C18" s="27"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㳞
+㳞
+–</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+꽃</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+南</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+나</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+△</t>
+        </is>
+      </c>
+      <c r="K18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="O18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
+      <c r="P18" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I18" s="26"/>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="Q18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M18" s="26"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O18" s="26"/>
-      <c r="P18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="S18" s="27"/>
+      <c r="S18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="T18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+無
+–</t>
+        </is>
+      </c>
+      <c r="U18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="B2:U2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -811,7 +811,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -821,7 +820,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -829,7 +827,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1064,7 +1061,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1074,7 +1070,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -1089,7 +1084,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -1098,17 +1093,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -1141,6 +1136,12 @@
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1233,7 +1234,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1283,6 +1284,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6653,976 +6694,976 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="6" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="17" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="6" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="U4" s="10" t="s">
+      <c r="U4" s="20" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="6" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="6" t="s">
+      <c r="F6" s="18"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="6" t="s">
+      <c r="I6" s="21"/>
+      <c r="J6" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="S6" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="T6" s="6" t="s">
+      <c r="T6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U6" s="11"/>
+      <c r="U6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="6" t="s">
+      <c r="L7" s="18"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="Q7" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="6" t="s">
+      <c r="S7" s="17"/>
+      <c r="T7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="7"/>
+      <c r="U7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="6" t="s">
+      <c r="L8" s="18"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="R8" s="6" t="s">
+      <c r="R8" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="6" t="s">
+      <c r="S8" s="20"/>
+      <c r="T8" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="6" t="s">
+      <c r="L9" s="18"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Q9" s="10" t="s">
+      <c r="Q9" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="S9" s="10"/>
-      <c r="T9" s="6" t="s">
+      <c r="S9" s="20"/>
+      <c r="T9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="U9" s="10"/>
+      <c r="U9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="6" t="s">
+      <c r="L10" s="18"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="6" t="s">
+      <c r="O10" s="21"/>
+      <c r="P10" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="R10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="6" t="s">
+      <c r="S10" s="21"/>
+      <c r="T10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="U10" s="11"/>
+      <c r="U10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="Q11" s="7" t="s">
+      <c r="Q11" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="R11" s="6" t="s">
+      <c r="R11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="S11" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="T11" s="6" t="s">
+      <c r="T11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="U11" s="17" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="Q12" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="U12" s="10" t="s">
+      <c r="U12" s="20" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="Q13" s="10" t="s">
+      <c r="Q13" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="S13" s="10" t="s">
+      <c r="S13" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="T13" s="6" t="s">
+      <c r="T13" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="U13" s="10" t="s">
+      <c r="U13" s="20" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="R14" s="6" t="s">
+      <c r="R14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="S14" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="T14" s="6" t="s">
+      <c r="T14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="U14" s="11" t="s">
+      <c r="U14" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="O15" s="7" t="s">
+      <c r="O15" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="Q15" s="7" t="s">
+      <c r="Q15" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="6" t="s">
+      <c r="R15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="S15" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T15" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="U15" s="7" t="s">
+      <c r="U15" s="17" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="6" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="Q16" s="10" t="s">
+      <c r="Q16" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="S16" s="10" t="s">
+      <c r="S16" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="T16" s="6" t="s">
+      <c r="T16" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="U16" s="10" t="s">
+      <c r="U16" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="6" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="10" t="s">
+      <c r="Q17" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="R17" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="S17" s="10" t="s">
+      <c r="S17" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="T17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="U17" s="10" t="s">
+      <c r="U17" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="22"/>
+      <c r="D18" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="21"/>
+      <c r="F18" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M18" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="O18" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="Q18" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="R18" s="6" t="s">
+      <c r="R18" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="S18" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="T18" s="6" t="s">
+      <c r="T18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="U18" s="21" t="s">
         <v>227</v>
       </c>
     </row>

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -1158,10 +1158,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -809,30 +809,8 @@
 요</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">–
+–㴌</t>
   </si>
   <si>
     <t xml:space="preserve">시
@@ -1059,22 +1037,8 @@
 왔</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+    <t xml:space="preserve">–
+△</t>
   </si>
 </sst>
 </file>
@@ -6685,7 +6649,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -6713,8 +6677,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -6738,7 +6702,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B3" s="16" t="s">
         <v>56</v>
       </c>
@@ -6796,7 +6760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B4" s="16" t="s">
         <v>59</v>
       </c>
@@ -6854,7 +6818,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B5" s="16" t="s">
         <v>62</v>
       </c>
@@ -6910,7 +6874,7 @@
       </c>
       <c r="U5" s="20"/>
     </row>
-    <row r="6" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B6" s="16" t="s">
         <v>63</v>
       </c>
@@ -6964,7 +6928,7 @@
       </c>
       <c r="U6" s="21"/>
     </row>
-    <row r="7" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B7" s="16" t="s">
         <v>66</v>
       </c>
@@ -7018,7 +6982,7 @@
       </c>
       <c r="U7" s="17"/>
     </row>
-    <row r="8" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B8" s="16" t="s">
         <v>69</v>
       </c>
@@ -7072,7 +7036,7 @@
       </c>
       <c r="U8" s="20"/>
     </row>
-    <row r="9" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B9" s="16" t="s">
         <v>71</v>
       </c>
@@ -7126,7 +7090,7 @@
       </c>
       <c r="U9" s="20"/>
     </row>
-    <row r="10" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B10" s="16" t="s">
         <v>221</v>
       </c>
@@ -7178,7 +7142,7 @@
       </c>
       <c r="U10" s="21"/>
     </row>
-    <row r="11" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B11" s="16" t="s">
         <v>75</v>
       </c>
@@ -7240,7 +7204,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B12" s="16" t="s">
         <v>77</v>
       </c>
@@ -7302,7 +7266,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B13" s="16" t="s">
         <v>80</v>
       </c>
@@ -7364,7 +7328,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B14" s="16" t="s">
         <v>83</v>
       </c>
@@ -7426,7 +7390,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B15" s="16" t="s">
         <v>53</v>
       </c>
@@ -7486,7 +7450,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
@@ -7546,7 +7510,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B17" s="16" t="s">
         <v>53</v>
       </c>
@@ -7606,7 +7570,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
       <c r="B18" s="18" t="s">
         <v>285</v>
       </c>
@@ -7670,7 +7634,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="67" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/꽃 타령 (자진모리).xlsx
+++ b/sheets/민요/검수/꽃 타령 (자진모리).xlsx
@@ -6655,30 +6655,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="14" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -6702,7 +6702,7 @@
       <c r="T2" s="15"/>
       <c r="U2" s="15"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B3" s="16" t="s">
         <v>56</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B4" s="16" t="s">
         <v>59</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B5" s="16" t="s">
         <v>62</v>
       </c>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="U5" s="20"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B6" s="16" t="s">
         <v>63</v>
       </c>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="U6" s="21"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B7" s="16" t="s">
         <v>66</v>
       </c>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="U7" s="17"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B8" s="16" t="s">
         <v>69</v>
       </c>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="U8" s="20"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B9" s="16" t="s">
         <v>71</v>
       </c>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="U9" s="20"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B10" s="16" t="s">
         <v>221</v>
       </c>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="U10" s="21"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B11" s="16" t="s">
         <v>75</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B12" s="16" t="s">
         <v>77</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B13" s="16" t="s">
         <v>80</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B14" s="16" t="s">
         <v>83</v>
       </c>
@@ -7390,7 +7390,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B15" s="16" t="s">
         <v>53</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B16" s="16" t="s">
         <v>53</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B17" s="16" t="s">
         <v>53</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="97.23" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
       <c r="B18" s="18" t="s">
         <v>285</v>
       </c>
@@ -7634,7 +7634,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
